--- a/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0006_ses-01_GMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0006_ses-01_GMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -12157,7 +12156,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="0">
-        <v>0.17103762827822106</v>
+        <v>0.17103762827822105</v>
       </c>
       <c r="L34" s="0">
         <v>0.05327650506126793</v>
@@ -13157,7 +13156,7 @@
         <v>0</v>
       </c>
       <c r="CY36" s="0">
-        <v>0.24313153415998035</v>
+        <v>0.24313153415998034</v>
       </c>
       <c r="CZ36" s="0">
         <v>0</v>
@@ -13414,7 +13413,7 @@
         <v>0</v>
       </c>
       <c r="BP37" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ37" s="0">
         <v>0</v>
@@ -13578,7 +13577,7 @@
         <v>0.144910035019925</v>
       </c>
       <c r="B38" s="0">
-        <v>6.2217762167586495</v>
+        <v>6.2217762167586494</v>
       </c>
       <c r="C38" s="0">
         <v>12.010605391073785</v>
@@ -13593,7 +13592,7 @@
         <v>11.732805371438399</v>
       </c>
       <c r="G38" s="0">
-        <v>8.2131410256410185</v>
+        <v>8.2131410256410184</v>
       </c>
       <c r="H38" s="0">
         <v>0.030275507114744145</v>
@@ -14177,7 +14176,7 @@
         <v>0.94488188976377863</v>
       </c>
       <c r="CC39" s="0">
-        <v>0.07499062617172847</v>
+        <v>0.074990626171728469</v>
       </c>
       <c r="CD39" s="0">
         <v>0</v>
@@ -14626,7 +14625,7 @@
         <v>3.8182696955050717</v>
       </c>
       <c r="DF40" s="0">
-        <v>1.8404907975460108</v>
+        <v>1.8404907975460107</v>
       </c>
       <c r="DG40" s="0">
         <v>0</v>
@@ -15080,7 +15079,7 @@
         <v>9.1668988576204988</v>
       </c>
       <c r="T42" s="0">
-        <v>2.5814382298709258</v>
+        <v>2.5814382298709257</v>
       </c>
       <c r="U42" s="0">
         <v>12.046848856664797</v>
@@ -15110,7 +15109,7 @@
         <v>0.070921985815602773</v>
       </c>
       <c r="AD42" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE42" s="0">
         <v>0</v>
@@ -15391,7 +15390,7 @@
         <v>1.7812343201204199</v>
       </c>
       <c r="C43" s="0">
-        <v>0.31816173221387512</v>
+        <v>0.31816173221387511</v>
       </c>
       <c r="D43" s="0">
         <v>0.0081960495041389983</v>
@@ -15472,7 +15471,7 @@
         <v>0.35460992907801386</v>
       </c>
       <c r="AD43" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE43" s="0">
         <v>0</v>
@@ -15646,10 +15645,10 @@
         <v>1.1314475873544083</v>
       </c>
       <c r="CJ43" s="0">
-        <v>0.6008855154965207</v>
+        <v>0.60088551549652069</v>
       </c>
       <c r="CK43" s="0">
-        <v>1.1749680715197946</v>
+        <v>1.1749680715197945</v>
       </c>
       <c r="CL43" s="0">
         <v>0.30314513073133736</v>
@@ -15813,7 +15812,7 @@
         <v>9.4209558823529331</v>
       </c>
       <c r="W44" s="0">
-        <v>0.20512820512820496</v>
+        <v>0.20512820512820495</v>
       </c>
       <c r="X44" s="0">
         <v>13.700966458214882</v>
@@ -15831,10 +15830,10 @@
         <v>0</v>
       </c>
       <c r="AC44" s="0">
-        <v>1.7021276595744666</v>
+        <v>1.7021276595744665</v>
       </c>
       <c r="AD44" s="0">
-        <v>1.0706638115631682</v>
+        <v>1.0706638115631681</v>
       </c>
       <c r="AE44" s="0">
         <v>0</v>
@@ -15849,7 +15848,7 @@
         <v>9.4909609895337681</v>
       </c>
       <c r="AI44" s="0">
-        <v>0.21283064761325613</v>
+        <v>0.21283064761325612</v>
       </c>
       <c r="AJ44" s="0">
         <v>0.77399380804953488</v>
@@ -15876,7 +15875,7 @@
         <v>6.0085836909871189</v>
       </c>
       <c r="AR44" s="0">
-        <v>14.915887850467279</v>
+        <v>14.915887850467278</v>
       </c>
       <c r="AS44" s="0">
         <v>0.19841269841269824</v>
@@ -15966,7 +15965,7 @@
         <v>1.9272614236866628</v>
       </c>
       <c r="BV44" s="0">
-        <v>1.3267813267813256</v>
+        <v>1.3267813267813255</v>
       </c>
       <c r="BW44" s="0">
         <v>0</v>
@@ -16418,7 +16417,7 @@
         <v>0.2188183807439823</v>
       </c>
       <c r="CZ45" s="0">
-        <v>1.6546259613143775</v>
+        <v>1.6546259613143774</v>
       </c>
       <c r="DA45" s="0">
         <v>0</v>
@@ -16609,7 +16608,7 @@
         <v>12.186978297161925</v>
       </c>
       <c r="AU46" s="0">
-        <v>1.6320474777448058</v>
+        <v>1.6320474777448057</v>
       </c>
       <c r="AV46" s="0">
         <v>2.3697742007601144</v>
@@ -16663,7 +16662,7 @@
         <v>0.43943446694688537</v>
       </c>
       <c r="BM46" s="0">
-        <v>3.47644707109334</v>
+        <v>3.4764470710933399</v>
       </c>
       <c r="BN46" s="0">
         <v>0.093138776777398249</v>
@@ -16911,7 +16910,7 @@
         <v>2.8140013726836095</v>
       </c>
       <c r="AA47" s="0">
-        <v>8.3553210202287112</v>
+        <v>8.3553210202287111</v>
       </c>
       <c r="AB47" s="0">
         <v>1.2262415695892148</v>
@@ -17007,7 +17006,7 @@
         <v>0.45814244064973142</v>
       </c>
       <c r="BG47" s="0">
-        <v>0.83179297597042901</v>
+        <v>0.831792975970429</v>
       </c>
       <c r="BH47" s="0">
         <v>0.90361445783132943</v>
@@ -17106,7 +17105,7 @@
         <v>10.564561207378473</v>
       </c>
       <c r="CN47" s="0">
-        <v>4.1995692749461791</v>
+        <v>4.199569274946179</v>
       </c>
       <c r="CO47" s="0">
         <v>0</v>
@@ -17285,10 +17284,10 @@
         <v>13.847251962883643</v>
       </c>
       <c r="AE48" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF48" s="0">
-        <v>2.5263157894736819</v>
+        <v>2.5263157894736818</v>
       </c>
       <c r="AG48" s="0">
         <v>0.022634676324128546</v>
@@ -17435,7 +17434,7 @@
         <v>0</v>
       </c>
       <c r="CC48" s="0">
-        <v>0.07499062617172847</v>
+        <v>0.074990626171728469</v>
       </c>
       <c r="CD48" s="0">
         <v>3.7692307692307656</v>
@@ -18015,7 +18014,7 @@
         <v>14.736842105263143</v>
       </c>
       <c r="AG50" s="0">
-        <v>2.4445450430058831</v>
+        <v>2.444545043005883</v>
       </c>
       <c r="AH50" s="0">
         <v>0.11893434823977153</v>
@@ -18048,7 +18047,7 @@
         <v>0.34334763948497821</v>
       </c>
       <c r="AR50" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS50" s="0">
         <v>9.3253968253968171</v>
@@ -18069,7 +18068,7 @@
         <v>2.4612579762989952</v>
       </c>
       <c r="AY50" s="0">
-        <v>4.5500505561172862</v>
+        <v>4.5500505561172861</v>
       </c>
       <c r="AZ50" s="0">
         <v>4.8351241200444566</v>
@@ -18368,7 +18367,7 @@
         <v>0.6382978723404249</v>
       </c>
       <c r="AD51" s="0">
-        <v>1.0706638115631682</v>
+        <v>1.0706638115631681</v>
       </c>
       <c r="AE51" s="0">
         <v>8.6065573770491728</v>
@@ -18467,7 +18466,7 @@
         <v>1.7689331122166927</v>
       </c>
       <c r="BK51" s="0">
-        <v>5.1308468988254648</v>
+        <v>5.1308468988254647</v>
       </c>
       <c r="BL51" s="0">
         <v>0</v>
@@ -18635,7 +18634,7 @@
         <v>3.7109374999999969</v>
       </c>
       <c r="DO51" s="0">
-        <v>0.97087378640776601</v>
+        <v>0.970873786407766</v>
       </c>
       <c r="DP51" s="0">
         <v>15.140845070422522</v>
@@ -19071,7 +19070,7 @@
         <v>0</v>
       </c>
       <c r="W53" s="0">
-        <v>0.20512820512820496</v>
+        <v>0.20512820512820495</v>
       </c>
       <c r="X53" s="0">
         <v>0</v>
@@ -19092,7 +19091,7 @@
         <v>0</v>
       </c>
       <c r="AD53" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE53" s="0">
         <v>15.368852459016381</v>
@@ -19101,7 +19100,7 @@
         <v>6.9473684210526248</v>
       </c>
       <c r="AG53" s="0">
-        <v>16.18379357175191</v>
+        <v>16.183793571751909</v>
       </c>
       <c r="AH53" s="0">
         <v>0</v>
@@ -19146,7 +19145,7 @@
         <v>0.74183976261127538</v>
       </c>
       <c r="AV53" s="0">
-        <v>0.17885088307623504</v>
+        <v>0.17885088307623503</v>
       </c>
       <c r="AW53" s="0">
         <v>0</v>
@@ -19460,7 +19459,7 @@
         <v>11.68032786885245</v>
       </c>
       <c r="AF54" s="0">
-        <v>2.7368421052631558</v>
+        <v>2.7368421052631557</v>
       </c>
       <c r="AG54" s="0">
         <v>14.191942055228598</v>
@@ -20789,7 +20788,7 @@
         <v>0</v>
       </c>
       <c r="DI57" s="0">
-        <v>27.102803738318031</v>
+        <v>27.10280373831803</v>
       </c>
       <c r="DJ57" s="0">
         <v>0</v>
@@ -20801,7 +20800,7 @@
         <v>0</v>
       </c>
       <c r="DM57" s="0">
-        <v>7.0512820512821231</v>
+        <v>7.051282051282123</v>
       </c>
       <c r="DN57" s="0">
         <v>0</v>
@@ -20905,7 +20904,7 @@
         <v>0</v>
       </c>
       <c r="AE58" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF58" s="0">
         <v>0</v>
@@ -24573,10 +24572,10 @@
         <v>0</v>
       </c>
       <c r="AU68" s="0">
-        <v>0.24109792284866447</v>
+        <v>0.24109792284866446</v>
       </c>
       <c r="AV68" s="0">
-        <v>0.17885088307623504</v>
+        <v>0.17885088307623503</v>
       </c>
       <c r="AW68" s="0">
         <v>0</v>
@@ -25363,7 +25362,7 @@
         <v>0</v>
       </c>
       <c r="BQ70" s="0">
-        <v>1.9023689877961219</v>
+        <v>1.9023689877961218</v>
       </c>
       <c r="BR70" s="0">
         <v>0</v>
@@ -25411,7 +25410,7 @@
         <v>0</v>
       </c>
       <c r="CG70" s="0">
-        <v>0.63818471902144947</v>
+        <v>0.63818471902144946</v>
       </c>
       <c r="CH70" s="0">
         <v>0</v>
@@ -25680,7 +25679,7 @@
         <v>0</v>
       </c>
       <c r="BB71" s="0">
-        <v>0.62093435836782907</v>
+        <v>0.62093435836782906</v>
       </c>
       <c r="BC71" s="0">
         <v>0</v>
@@ -25973,7 +25972,7 @@
         <v>0</v>
       </c>
       <c r="AE72" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF72" s="0">
         <v>0</v>
@@ -26192,7 +26191,7 @@
         <v>0</v>
       </c>
       <c r="CZ72" s="0">
-        <v>5.5464926590538291</v>
+        <v>5.546492659053829</v>
       </c>
       <c r="DA72" s="0">
         <v>0</v>
@@ -26446,7 +26445,7 @@
         <v>1.3508949679162432</v>
       </c>
       <c r="BP73" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ73" s="0">
         <v>11.629576453697046</v>
@@ -26467,7 +26466,7 @@
         <v>0</v>
       </c>
       <c r="BW73" s="0">
-        <v>0.043859649122806981</v>
+        <v>0.04385964912280698</v>
       </c>
       <c r="BX73" s="0">
         <v>0</v>
@@ -26533,7 +26532,7 @@
         <v>8.5330776605944312</v>
       </c>
       <c r="CS73" s="0">
-        <v>0.044228217602830571</v>
+        <v>0.04422821760283057</v>
       </c>
       <c r="CT73" s="0">
         <v>0.020024028834601505</v>
@@ -26931,7 +26930,7 @@
         <v>0.23679417122040053</v>
       </c>
       <c r="DE74" s="0">
-        <v>0.1449975833736103</v>
+        <v>0.14499758337361029</v>
       </c>
       <c r="DF74" s="0">
         <v>0</v>
@@ -27176,7 +27175,7 @@
         <v>4.307250538406314</v>
       </c>
       <c r="BR75" s="0">
-        <v>4.964882538144825</v>
+        <v>4.9648825381448249</v>
       </c>
       <c r="BS75" s="0">
         <v>3.3927056827820152</v>
@@ -27460,7 +27459,7 @@
         <v>2.5751072961373369</v>
       </c>
       <c r="AR76" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS76" s="0">
         <v>0</v>
@@ -27496,7 +27495,7 @@
         <v>0.90147282884712976</v>
       </c>
       <c r="BD76" s="0">
-        <v>0.020554984583761545</v>
+        <v>0.020554984583761544</v>
       </c>
       <c r="BE76" s="0">
         <v>0</v>
@@ -27511,7 +27510,7 @@
         <v>10.525435073627836</v>
       </c>
       <c r="BI76" s="0">
-        <v>0.032275416890801476</v>
+        <v>0.032275416890801475</v>
       </c>
       <c r="BJ76" s="0">
         <v>6.5008291873963469</v>
@@ -27804,7 +27803,7 @@
         <v>0.49030532649877384</v>
       </c>
       <c r="AL77" s="0">
-        <v>0.79319017218030497</v>
+        <v>0.79319017218030496</v>
       </c>
       <c r="AM77" s="0">
         <v>12.140871177015745</v>
@@ -27870,7 +27869,7 @@
         <v>8.7615526802218024</v>
       </c>
       <c r="BH77" s="0">
-        <v>7.9149933065595644</v>
+        <v>7.9149933065595643</v>
       </c>
       <c r="BI77" s="0">
         <v>0.11834319526627209</v>
@@ -27927,7 +27926,7 @@
         <v>10.466034755134272</v>
       </c>
       <c r="CA77" s="0">
-        <v>8.7218045112781884</v>
+        <v>8.7218045112781883</v>
       </c>
       <c r="CB77" s="0">
         <v>0</v>
@@ -27936,7 +27935,7 @@
         <v>0</v>
       </c>
       <c r="CD77" s="0">
-        <v>4.6538461538461498</v>
+        <v>4.6538461538461497</v>
       </c>
       <c r="CE77" s="0">
         <v>1.1428571428571419</v>
@@ -27960,7 +27959,7 @@
         <v>8.6249467858663191</v>
       </c>
       <c r="CL77" s="0">
-        <v>4.7934823796892721</v>
+        <v>4.793482379689272</v>
       </c>
       <c r="CM77" s="0">
         <v>7.6579094466182154</v>
@@ -28432,7 +28431,7 @@
         <v>0.074759368283337943</v>
       </c>
       <c r="F79" s="0">
-        <v>0.068864594990100656</v>
+        <v>0.068864594990100655</v>
       </c>
       <c r="G79" s="0">
         <v>0</v>
@@ -28510,7 +28509,7 @@
         <v>4.9180327868852416</v>
       </c>
       <c r="AF79" s="0">
-        <v>4.8421052631578903</v>
+        <v>4.8421052631578902</v>
       </c>
       <c r="AG79" s="0">
         <v>0.022634676324128546</v>
@@ -28594,7 +28593,7 @@
         <v>5.6007393715341909</v>
       </c>
       <c r="BH79" s="0">
-        <v>1.8239625167335996</v>
+        <v>1.8239625167335995</v>
       </c>
       <c r="BI79" s="0">
         <v>2.8832705755782655</v>
@@ -28660,7 +28659,7 @@
         <v>0</v>
       </c>
       <c r="CD79" s="0">
-        <v>0.42307692307692269</v>
+        <v>0.42307692307692268</v>
       </c>
       <c r="CE79" s="0">
         <v>5.1428571428571379</v>
@@ -28699,13 +28698,13 @@
         <v>0</v>
       </c>
       <c r="CQ79" s="0">
-        <v>8.6801040312093552</v>
+        <v>8.6801040312093551</v>
       </c>
       <c r="CR79" s="0">
         <v>0</v>
       </c>
       <c r="CS79" s="0">
-        <v>9.9071207430340476</v>
+        <v>9.9071207430340475</v>
       </c>
       <c r="CT79" s="0">
         <v>12.054465358430106</v>
@@ -28729,7 +28728,7 @@
         <v>0.11652295502213926</v>
       </c>
       <c r="DA79" s="0">
-        <v>2.7377521613832832</v>
+        <v>2.7377521613832831</v>
       </c>
       <c r="DB79" s="0">
         <v>0</v>
@@ -28962,7 +28961,7 @@
         <v>6.5303926842388318</v>
       </c>
       <c r="BJ80" s="0">
-        <v>0.022111663902708662</v>
+        <v>0.022111663902708661</v>
       </c>
       <c r="BK80" s="0">
         <v>0</v>
@@ -29001,7 +29000,7 @@
         <v>0</v>
       </c>
       <c r="BW80" s="0">
-        <v>4.0789473684210496</v>
+        <v>4.0789473684210495</v>
       </c>
       <c r="BX80" s="0">
         <v>1.1358855700462758</v>
@@ -29019,7 +29018,7 @@
         <v>1.8897637795275573</v>
       </c>
       <c r="CC80" s="0">
-        <v>0.07499062617172847</v>
+        <v>0.074990626171728469</v>
       </c>
       <c r="CD80" s="0">
         <v>0</v>
@@ -29103,7 +29102,7 @@
         <v>5.4098360655737654</v>
       </c>
       <c r="DE80" s="0">
-        <v>8.1681971967133809</v>
+        <v>8.1681971967133808</v>
       </c>
       <c r="DF80" s="0">
         <v>9.6625766871165553</v>
@@ -29444,7 +29443,7 @@
         <v>1.4925373134328344</v>
       </c>
       <c r="CX81" s="0">
-        <v>4.6021093000958731</v>
+        <v>4.602109300095873</v>
       </c>
       <c r="CY81" s="0">
         <v>5.1057622173595867</v>
@@ -29483,7 +29482,7 @@
         <v>11.178861788617876</v>
       </c>
       <c r="DK81" s="0">
-        <v>0.62413314840499246</v>
+        <v>0.62413314840499245</v>
       </c>
       <c r="DL81" s="0">
         <v>0</v>
@@ -29527,7 +29526,7 @@
         <v>0.060551014229488963</v>
       </c>
       <c r="I82" s="0">
-        <v>0.23255813953488611</v>
+        <v>0.2325581395348861</v>
       </c>
       <c r="J82" s="0">
         <v>0</v>
@@ -29542,7 +29541,7 @@
         <v>9.5218295218296198</v>
       </c>
       <c r="N82" s="0">
-        <v>0.31152647975078202</v>
+        <v>0.31152647975078201</v>
       </c>
       <c r="O82" s="0">
         <v>0</v>
@@ -29650,7 +29649,7 @@
         <v>1.5608180839612646</v>
       </c>
       <c r="AX82" s="0">
-        <v>4.9225159525980447</v>
+        <v>4.9225159525980446</v>
       </c>
       <c r="AY82" s="0">
         <v>0</v>
@@ -29683,7 +29682,7 @@
         <v>0</v>
       </c>
       <c r="BI82" s="0">
-        <v>8.9618074233459773</v>
+        <v>8.9618074233459772</v>
       </c>
       <c r="BJ82" s="0">
         <v>0</v>
@@ -29740,7 +29739,7 @@
         <v>0.75187969924812792</v>
       </c>
       <c r="CB82" s="0">
-        <v>9.1338582677166294</v>
+        <v>9.1338582677166293</v>
       </c>
       <c r="CC82" s="0">
         <v>1.6872890888639094</v>
@@ -29764,7 +29763,7 @@
         <v>8.9850249584027537</v>
       </c>
       <c r="CJ82" s="0">
-        <v>6.1037318153068299</v>
+        <v>6.1037318153068298</v>
       </c>
       <c r="CK82" s="0">
         <v>0.61302681992337793</v>
@@ -29806,7 +29805,7 @@
         <v>0.40043684018930148</v>
       </c>
       <c r="CX82" s="0">
-        <v>8.0057526366252017</v>
+        <v>8.0057526366252016</v>
       </c>
       <c r="CY82" s="0">
         <v>9.7495745198153188</v>
@@ -29827,7 +29826,7 @@
         <v>0.49180327868852963</v>
       </c>
       <c r="DE82" s="0">
-        <v>1.0633156114064875</v>
+        <v>1.0633156114064874</v>
       </c>
       <c r="DF82" s="0">
         <v>0.81799591002045835</v>
@@ -29934,7 +29933,7 @@
         <v>0</v>
       </c>
       <c r="X83" s="0">
-        <v>5.1165434906196659</v>
+        <v>5.1165434906196658</v>
       </c>
       <c r="Y83" s="0">
         <v>0</v>
@@ -30153,7 +30152,7 @@
         <v>0</v>
       </c>
       <c r="CS83" s="0">
-        <v>0.044228217602830571</v>
+        <v>0.04422821760283057</v>
       </c>
       <c r="CT83" s="0">
         <v>0.18021625951141354</v>
@@ -30305,7 +30304,7 @@
         <v>8.9910775566231909</v>
       </c>
       <c r="AA84" s="0">
-        <v>5.2770448548812619</v>
+        <v>5.2770448548812618</v>
       </c>
       <c r="AB84" s="0">
         <v>0</v>
@@ -30428,7 +30427,7 @@
         <v>0</v>
       </c>
       <c r="BP84" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ84" s="0">
         <v>0</v>
@@ -30476,7 +30475,7 @@
         <v>0.57142857142857095</v>
       </c>
       <c r="CF84" s="0">
-        <v>2.2452504317789273</v>
+        <v>2.2452504317789272</v>
       </c>
       <c r="CG84" s="0">
         <v>0</v>
@@ -30488,7 +30487,7 @@
         <v>2.1630615640598982</v>
       </c>
       <c r="CJ84" s="0">
-        <v>0.6008855154965207</v>
+        <v>0.60088551549652069</v>
       </c>
       <c r="CK84" s="0">
         <v>0.0085142613878245992</v>
@@ -30503,7 +30502,7 @@
         <v>8.9016511127063822</v>
       </c>
       <c r="CO84" s="0">
-        <v>1.7191219254165549</v>
+        <v>1.7191219254165548</v>
       </c>
       <c r="CP84" s="0">
         <v>0</v>
@@ -30826,7 +30825,7 @@
         <v>0</v>
       </c>
       <c r="CB85" s="0">
-        <v>6.1417322834645614</v>
+        <v>6.1417322834645613</v>
       </c>
       <c r="CC85" s="0">
         <v>10.873640794900629</v>
@@ -30907,7 +30906,7 @@
         <v>4.9373040752351054</v>
       </c>
       <c r="DC85" s="0">
-        <v>0.20206555904804655</v>
+        <v>0.20206555904804654</v>
       </c>
       <c r="DD85" s="0">
         <v>0</v>
@@ -30969,7 +30968,7 @@
         <v>6.0170439872600445</v>
       </c>
       <c r="G86" s="0">
-        <v>8.1730769230769163</v>
+        <v>8.1730769230769162</v>
       </c>
       <c r="H86" s="0">
         <v>8.5376930063578484</v>
@@ -31191,7 +31190,7 @@
         <v>1.1023622047244084</v>
       </c>
       <c r="CC86" s="0">
-        <v>9.4113235845519228</v>
+        <v>9.4113235845519227</v>
       </c>
       <c r="CD86" s="0">
         <v>0</v>
@@ -31233,7 +31232,7 @@
         <v>0</v>
       </c>
       <c r="CQ86" s="0">
-        <v>0.032509752925877739</v>
+        <v>0.032509752925877738</v>
       </c>
       <c r="CR86" s="0">
         <v>0</v>
@@ -31245,7 +31244,7 @@
         <v>0</v>
       </c>
       <c r="CU86" s="0">
-        <v>4.491017964071852</v>
+        <v>4.4910179640718519</v>
       </c>
       <c r="CV86" s="0">
         <v>0</v>
@@ -31340,10 +31339,10 @@
         <v>9.086378737541521</v>
       </c>
       <c r="J87" s="0">
-        <v>2.6472280836370588</v>
+        <v>2.6472280836370587</v>
       </c>
       <c r="K87" s="0">
-        <v>0.91220068415051237</v>
+        <v>0.91220068415051236</v>
       </c>
       <c r="L87" s="0">
         <v>3.676078849227487</v>
@@ -31442,7 +31441,7 @@
         <v>0</v>
       </c>
       <c r="AR87" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS87" s="0">
         <v>0</v>
@@ -31702,13 +31701,13 @@
         <v>5.4485049833886992</v>
       </c>
       <c r="J88" s="0">
-        <v>6.2344139650872768</v>
+        <v>6.2344139650872767</v>
       </c>
       <c r="K88" s="0">
         <v>0.11402508551881405</v>
       </c>
       <c r="L88" s="0">
-        <v>1.1188066062866267</v>
+        <v>1.1188066062866266</v>
       </c>
       <c r="M88" s="0">
         <v>0.041580041580041548</v>
@@ -31729,7 +31728,7 @@
         <v>0</v>
       </c>
       <c r="S88" s="0">
-        <v>2.2290331568682063</v>
+        <v>2.2290331568682062</v>
       </c>
       <c r="T88" s="0">
         <v>5.429215324728534</v>
@@ -32806,7 +32805,7 @@
         <v>7.5341111330828499</v>
       </c>
       <c r="P91" s="0">
-        <v>0.23886708752772543</v>
+        <v>0.23886708752772542</v>
       </c>
       <c r="Q91" s="0">
         <v>0.15432098765432084</v>
